--- a/Notes/notes-WILD_data.xlsx
+++ b/Notes/notes-WILD_data.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12152" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12213" uniqueCount="1378">
   <si>
     <t>; Johto Pokémon in grass</t>
   </si>
@@ -4053,13 +4053,94 @@
   </si>
   <si>
     <t>SENTRET</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_NONE</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_POND</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_REMORAID</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_LAKE</t>
+  </si>
+  <si>
+    <t>GOLDEEN</t>
+  </si>
+  <si>
+    <t>SEAKING</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_SHORE</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_STARYU</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_SHELLDER</t>
+  </si>
+  <si>
+    <t>TENTACOOL</t>
+  </si>
+  <si>
+    <t>CORSOLA / STARYU</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_OCEAN</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_HORSEA</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_CHINCHOU</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_GYARADOS</t>
+  </si>
+  <si>
+    <t>GYARADOS</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_DRATINI_NO_SWARM</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_DRATINI</t>
+  </si>
+  <si>
+    <t>DRAGONAIR</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_QWILFISH_NO_SWARM</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_QWILFISH</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_WHIRL_ISLANDS</t>
+  </si>
+  <si>
+    <t>SEADRA</t>
+  </si>
+  <si>
+    <t>up to +4</t>
+  </si>
+  <si>
+    <t>engine\events\fish.asm</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>const FISHGROUP_CHINCHOU_LAKE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4082,13 +4163,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
+      <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4097,12 +4185,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4110,21 +4210,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4132,60 +4241,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -4198,12 +4288,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF9C0006"/>
       </font>
     </dxf>
   </dxfs>
@@ -4544,533 +4629,1074 @@
   <dimension ref="B2:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="3.140625" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="11"/>
+    <col min="6" max="6" width="3.140625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="8.7109375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="12" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="3"/>
+    <col min="10" max="10" width="17.7109375" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="17"/>
-      <c r="C2" s="4">
+      <c r="B2" s="12"/>
+      <c r="C2" s="6">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>1350</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>1287</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="6">
         <v>29</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>1288</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1007</v>
       </c>
       <c r="C3" s="6">
         <v>3</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="5" t="s">
         <v>1006</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>1290</v>
       </c>
       <c r="I3" s="6">
+        <v>30</v>
+      </c>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="12"/>
+      <c r="C4" s="6">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="6">
         <v>31</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J4" s="11" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="17"/>
-      <c r="C4" s="4">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7" t="s">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C5" s="6">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>1293</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I5" s="6">
         <v>32</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J5" s="11" t="s">
         <v>1305</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C5" s="4">
-        <v>5</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1289</v>
-      </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="4">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C6" s="6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="6">
         <v>33</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J6" s="5" t="s">
         <v>1295</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C6" s="4">
-        <v>6</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="H6" s="2" t="s">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C7" s="6">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>1297</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I7" s="6">
         <v>35</v>
       </c>
-      <c r="J6" s="23"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C7" s="4">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C8" s="6">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>1298</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I8" s="6">
         <v>37</v>
       </c>
-      <c r="J7" s="23"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C8" s="4">
-        <v>8</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>1294</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>1299</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I9" s="6">
         <v>38</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J9" s="11" t="s">
         <v>1301</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="4">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C10" s="6">
+        <v>11</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="6">
         <v>39</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C10" s="4">
-        <v>11</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H10" s="7" t="s">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="12"/>
+      <c r="C11" s="6">
+        <v>12</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>1303</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I11" s="6">
         <v>41</v>
       </c>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="19"/>
-      <c r="C11" s="15">
-        <v>12</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>1293</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C12" s="6">
+        <v>13</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I12" s="6">
         <v>42</v>
       </c>
-      <c r="J11" s="22"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C12" s="16">
-        <v>13</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="4">
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="12"/>
+      <c r="C13" s="6">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="6">
         <v>43</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J13" s="11" t="s">
         <v>1306</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="17"/>
-      <c r="C13" s="4">
-        <v>15</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>1029</v>
-      </c>
-      <c r="H13" s="7" t="s">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C14" s="6">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>1307</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I14" s="6">
         <v>44</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J14" s="11" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C14" s="4">
-        <v>16</v>
-      </c>
-      <c r="D14" s="3" t="s">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C15" s="6">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>1343</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>1308</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I15" s="6">
         <v>45</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J15" s="11" t="s">
         <v>1309</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C15" s="4">
-        <v>17</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>1300</v>
-      </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="4">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C16" s="6">
+        <v>19</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="6">
         <v>46</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J16" s="11" t="s">
         <v>1311</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C16" s="8">
-        <v>19</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="H16" s="2" t="s">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C17" s="6">
+        <v>20</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="H17" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>1335</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C18" s="6">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="6" t="s">
+        <v>1331</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C19" s="6">
+        <v>22</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C20" s="6">
+        <v>24</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="H20" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>1325</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="12"/>
+      <c r="C21" s="6">
+        <v>26</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="6" t="s">
+        <v>1323</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="6" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="H24" s="3" t="s">
         <v>1313</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I24" s="6" t="s">
         <v>1314</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J24" s="11" t="s">
         <v>1315</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C17" s="8">
-        <v>20</v>
-      </c>
-      <c r="D17" s="21"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="4" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C18" s="4">
-        <v>21</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>1321</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>1320</v>
-      </c>
-      <c r="J18" s="23"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C19" s="4">
-        <v>22</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="4" t="s">
-        <v>1323</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C20" s="4">
-        <v>24</v>
-      </c>
-      <c r="D20" s="18"/>
-      <c r="H20" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>1325</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="17"/>
-      <c r="C21" s="4">
-        <v>26</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>1328</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>1047</v>
-      </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="4" t="s">
-        <v>1331</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>1312</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>1334</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>1335</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>1347</v>
-      </c>
-      <c r="K23" s="11"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="H24" s="7" t="s">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="12"/>
+      <c r="C26" s="6" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H26" s="9" t="s">
         <v>1345</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I26" s="6" t="s">
         <v>1344</v>
       </c>
-      <c r="J24" s="23"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>1339</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>1338</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="17"/>
-      <c r="C26" s="4" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>1342</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>1340</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I27" s="6" t="s">
         <v>1341</v>
       </c>
-      <c r="J26" s="24"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>1322</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>1324</v>
       </c>
-      <c r="D28" s="20"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>1326</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="5" t="s">
         <v>1207</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
         <v>1052</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>1329</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="5" t="s">
         <v>1330</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
         <v>1332</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>1333</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="5" t="s">
         <v>1346</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B14:B20 B1 B22:B25 B27:B31 B33:B1048576 B3:B12 D1 D14:D20 D22:D25 D27:D31 D33:D1048576 D3:D12 H1:H1048576 J1:J1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="34"/>
+  <conditionalFormatting sqref="B1:B1048576 D1:D1048576 H1:H2 H34:H1048576 H4:H27 J1:J2 J34:J1048576 J4:J27">
+    <cfRule type="duplicateValues" dxfId="2" priority="164"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B25 B1 B27:B31 B33:B1048576 B3:B20 D1 D22:D25 D27:D31 D33:D1048576 D3:D20 H1:H1048576 J1:J1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="50"/>
+  <conditionalFormatting sqref="B14:B20 B1 B22:B25 B27:B31 B33:B1048576 B3:B12 D1 D14:D20 D22:D25 D27:D31 D33:D1048576 D3:D12 H1:H2 H34:H1048576 H4:H27 J1:J2 J34:J1048576 J4:J27">
+    <cfRule type="duplicateValues" dxfId="1" priority="174"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576 D1:D1048576 H1:H1048576 J1:J1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B22:B25 B1 B27:B31 B33:B1048576 B3:B20 D1 D22:D25 D27:D31 D33:D1048576 D3:D20 H1:H2 H34:H1048576 H4:H27 J1:J2 J34:J1048576 J4:J27">
+    <cfRule type="duplicateValues" dxfId="0" priority="194"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{020CF180-D95C-4B79-8F14-EF3008FC37B9}">
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="16" customWidth="1"/>
+    <col min="4" max="6" width="4.7109375" style="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="16" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" s="17" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="16" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>60</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D4" s="17">
+        <v>5</v>
+      </c>
+      <c r="E4" s="17">
+        <v>10</v>
+      </c>
+      <c r="F4" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>20</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D5" s="17">
+        <v>5</v>
+      </c>
+      <c r="E5" s="17">
+        <v>10</v>
+      </c>
+      <c r="F5" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>10</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D6" s="17">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17">
+        <v>10</v>
+      </c>
+      <c r="F6" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>10</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F7" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>60</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D10" s="17">
+        <v>20</v>
+      </c>
+      <c r="E10" s="17">
+        <v>20</v>
+      </c>
+      <c r="F10" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>20</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D11" s="17">
+        <v>15</v>
+      </c>
+      <c r="E11" s="17">
+        <v>15</v>
+      </c>
+      <c r="F11" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>10</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D12" s="17">
+        <v>20</v>
+      </c>
+      <c r="E12" s="17">
+        <v>20</v>
+      </c>
+      <c r="F12" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>10</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F13" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="16" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>60</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D16" s="17">
+        <v>5</v>
+      </c>
+      <c r="E16" s="17">
+        <v>10</v>
+      </c>
+      <c r="F16" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>20</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D17" s="17">
+        <v>5</v>
+      </c>
+      <c r="E17" s="17">
+        <v>10</v>
+      </c>
+      <c r="F17" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>10</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D18" s="17">
+        <v>5</v>
+      </c>
+      <c r="E18" s="17">
+        <v>10</v>
+      </c>
+      <c r="F18" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>10</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F19" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="16" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>60</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F22" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="15">
+        <v>20</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F23" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="15">
+        <v>10</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F24" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
+        <v>10</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F25" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="16" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="16" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="16" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
+        <v>40</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="15">
+        <v>30</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="15">
+        <v>10</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="16" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="16" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="16" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="15">
+        <v>50</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
+        <v>30</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
+        <v>10</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
+        <v>10</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="16" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="15">
+        <v>30</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="15">
+        <v>30</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="15">
+        <v>30</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="15">
+        <v>10</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="16" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="16" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="15">
+        <v>40</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
+        <v>48</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
+        <v>10</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>2</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="16" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="16" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="15">
+        <v>60</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="15">
+        <v>20</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="15">
+        <v>10</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="15">
+        <v>10</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="16" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="15">
+        <v>40</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="15">
+        <v>30</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="15">
+        <v>20</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="15">
+        <v>10</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>